--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -493,28 +493,28 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.878599221789883</v>
+        <v>1195.514583657588</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>415.311230062179</v>
       </c>
       <c r="F2" t="n">
-        <v>2.444731738849386</v>
+        <v>993.0958241758242</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>3.897787144362487</v>
+        <v>1618.794773445732</v>
       </c>
       <c r="I2" t="n">
-        <v>-47.91561058005993</v>
+        <v>291.7242061765025</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -531,24 +531,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35.62818336162988</v>
+        <v>591.7102886247877</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>16.60792756730998</v>
       </c>
       <c r="F3" t="n">
-        <v>9.101031553398059</v>
+        <v>58.78737257281553</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>16.97815533980582</v>
+        <v>281.9719741100324</v>
       </c>
       <c r="I3" t="n">
-        <v>544.6441597306909</v>
+        <v>396.8917496227702</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -569,28 +569,28 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.420637528754519</v>
+        <v>30.8787331580677</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4.809293940014331</v>
       </c>
       <c r="F4" t="n">
-        <v>7.513567983876772</v>
+        <v>18.22773842942489</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>16.13377374071016</v>
+        <v>77.5920602807597</v>
       </c>
       <c r="I4" t="n">
-        <v>16.17281865448299</v>
+        <v>-89.88222527819487</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -607,28 +607,28 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5.100622406639004</v>
+        <v>264.788786307054</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>51.91303437055115</v>
       </c>
       <c r="F5" t="n">
-        <v>9.221234567901234</v>
+        <v>71.03342962962964</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>10.10688591983556</v>
+        <v>524.679116135663</v>
       </c>
       <c r="I5" t="n">
-        <v>-7.711083328136459</v>
+        <v>122.3577413439793</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -645,28 +645,28 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.417017345786719</v>
+        <v>69.3418875089808</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>12.80075050210315</v>
       </c>
       <c r="F6" t="n">
-        <v>5.956772502184678</v>
+        <v>42.24107253131372</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>5.417017345786719</v>
+        <v>69.3418875089808</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.986341552231585</v>
+        <v>-77.2793270692416</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -676,31 +676,35 @@
           <t>ADANIPOWER</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Adani Power Ltd</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3.400993220873404</v>
+        <v>108.1651860318461</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>31.8039993046703</v>
       </c>
       <c r="F7" t="n">
-        <v>3.709086572859528</v>
+        <v>67.10229191509659</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>4.022093782045307</v>
+        <v>127.9186678474877</v>
       </c>
       <c r="I7" t="n">
-        <v>-38.46359229528187</v>
+        <v>-9.167730274641483</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -717,24 +721,24 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.70937742185482</v>
+        <v>331.0284267631103</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>30.91014666152065</v>
       </c>
       <c r="F8" t="n">
-        <v>7.240638955685331</v>
+        <v>220.2181449673652</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>11.17111290757208</v>
+        <v>345.3007383454595</v>
       </c>
       <c r="I8" t="n">
-        <v>93.77181090814413</v>
+        <v>126.6282033396705</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -750,33 +754,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Apollo Hospitals</t>
+          <t>Apollo Hospitals
+Chain of Indian private hospitals</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.666666666666667</v>
+        <v>1556.881070261438</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>274.7437182814302</v>
       </c>
       <c r="F9" t="n">
-        <v>4.469581056466303</v>
+        <v>696.1586265938068</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>7.418181818181818</v>
+        <v>2038.098855614973</v>
       </c>
       <c r="I9" t="n">
-        <v>2.530727843434333</v>
+        <v>134.4970534387903</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -788,33 +793,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Asian Paints</t>
+          <t>Asian Paints
+Indian Multi-National Paint and Coating Manufacturing Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.044050960915569</v>
+        <v>459.2367048153747</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>113.5585850064075</v>
       </c>
       <c r="F10" t="n">
-        <v>3.173477024397545</v>
+        <v>318.6946834306242</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>4.464362336114422</v>
+        <v>506.9666698450537</v>
       </c>
       <c r="I10" t="n">
-        <v>-26.82832556612708</v>
+        <v>214.4019694550812</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -831,28 +837,28 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.359281437125748</v>
+        <v>2298.806002994012</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>428.939220670391</v>
       </c>
       <c r="F11" t="n">
-        <v>4.455333911535126</v>
+        <v>1333.182489158716</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>6.556776556776557</v>
+        <v>2812.458626373626</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.030995329474762</v>
+        <v>1830.434131077522</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -873,24 +879,24 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.950996740695824</v>
+        <v>35.96106382172364</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>6.042863975341192</v>
       </c>
       <c r="F12" t="n">
-        <v>32.5881838172598</v>
+        <v>50.35611519992819</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>12.05550863723608</v>
+        <v>72.84979884836852</v>
       </c>
       <c r="I12" t="n">
-        <v>5.06021307302118</v>
+        <v>-60.87434664352666</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -907,28 +913,28 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.929181929181929</v>
+        <v>88.70130240130241</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>22.57500517920033</v>
       </c>
       <c r="F13" t="n">
-        <v>3.376790987640818</v>
+        <v>71.71927157388167</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>4.697048329549141</v>
+        <v>106.0358903665261</v>
       </c>
       <c r="I13" t="n">
-        <v>-28.90672652441896</v>
+        <v>-63.58341437646571</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -945,28 +951,28 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.65181598062954</v>
+        <v>115.3215599273608</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>31.57923634133404</v>
       </c>
       <c r="F14" t="n">
-        <v>7.679610369621144</v>
+        <v>48.24303898502605</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>4.940868140868141</v>
+        <v>156.0288427518427</v>
       </c>
       <c r="I14" t="n">
-        <v>-33.92529109807678</v>
+        <v>25.46990824893287</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -983,28 +989,28 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7.991317125300561</v>
+        <v>292.7555610472883</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>36.63420640890627</v>
       </c>
       <c r="F15" t="n">
-        <v>38.52638352638353</v>
+        <v>1410.305746460746</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>12.09522846744844</v>
+        <v>443.0990962393853</v>
       </c>
       <c r="I15" t="n">
-        <v>44.59215787378257</v>
+        <v>218.5181800099222</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -1025,24 +1031,24 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.983819611410748</v>
+        <v>160.7168483982065</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>32.24772582664024</v>
       </c>
       <c r="F16" t="n">
-        <v>19.53449823153672</v>
+        <v>146.0496003800876</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>6.664581160931526</v>
+        <v>214.9175860271116</v>
       </c>
       <c r="I16" t="n">
-        <v>-12.01454594796292</v>
+        <v>74.86000219978226</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -1063,24 +1069,24 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5.942861397934869</v>
+        <v>29.33732227958697</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4.936565118241127</v>
       </c>
       <c r="F17" t="n">
-        <v>33.86801265632063</v>
+        <v>44.0115374846639</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>7.978207264245252</v>
+        <v>39.38493968677108</v>
       </c>
       <c r="I17" t="n">
-        <v>4.916589932036564</v>
+        <v>-68.08098037342086</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1097,28 +1103,28 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.01849812816560229</v>
+        <v>298.3442105263158</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>16128.34595238095</v>
       </c>
       <c r="F18" t="n">
-        <v>0.02224947442186405</v>
+        <v>237.3553013314646</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>0.02813127930341594</v>
+        <v>453.7110046885466</v>
       </c>
       <c r="I18" t="n">
-        <v>-99.66530119801877</v>
+        <v>-2.244062403466862</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1135,28 +1141,28 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>5.979950781702374</v>
+        <v>27.40343297625941</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4.582551592248756</v>
       </c>
       <c r="F19" t="n">
-        <v>3.693793120533115</v>
+        <v>7.360036540200414</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>6.724098640839912</v>
+        <v>30.81352893301864</v>
       </c>
       <c r="I19" t="n">
-        <v>8.199183432210333</v>
+        <v>-94.78366812534259</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1173,24 +1179,24 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>54.37977528089888</v>
+        <v>1213.604157303371</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>22.31719699161122</v>
       </c>
       <c r="F20" t="n">
-        <v>31.74</v>
+        <v>523.0303333333333</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>54.37977528089888</v>
+        <v>1213.604157303371</v>
       </c>
       <c r="I20" t="n">
-        <v>883.9290481493458</v>
+        <v>297.6514645916918</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1211,28 +1217,28 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.788867562380038</v>
+        <v>1247.387739923224</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>215.4804418103448</v>
       </c>
       <c r="F21" t="n">
-        <v>5.461642599277979</v>
+        <v>1173.102459386281</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>8.47191011235955</v>
+        <v>1825.530933988764</v>
       </c>
       <c r="I21" t="n">
-        <v>4.741789040012834</v>
+        <v>412.1187762401337</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -1249,28 +1255,28 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.507135575942915</v>
+        <v>34.12422673656619</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>6.196365835922522</v>
       </c>
       <c r="F22" t="n">
-        <v>4.904496497702794</v>
+        <v>19.7055483166378</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>5.507135575942915</v>
+        <v>34.12422673656619</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.3557731293121202</v>
+        <v>-71.34400558242014</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1287,28 +1293,28 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.8511038046031</v>
+        <v>152.5344011272898</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>82.40186247145394</v>
       </c>
       <c r="F23" t="n">
-        <v>1.915178571428571</v>
+        <v>104.2126084183673</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>1.8511038046031</v>
+        <v>152.5344011272898</v>
       </c>
       <c r="I23" t="n">
-        <v>-66.50676110593419</v>
+        <v>198.9325346106328</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -1329,24 +1335,24 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>5.559893790356647</v>
+        <v>29.95690543720958</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>5.388035557292175</v>
       </c>
       <c r="F24" t="n">
-        <v>30.44003248240536</v>
+        <v>38.85803273227002</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>8.121022476862054</v>
+        <v>43.75635786690172</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.844404940820432</v>
+        <v>-67.40687362366427</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1367,24 +1373,24 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5.086448598130841</v>
+        <v>252.318785046729</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>49.60608176389527</v>
       </c>
       <c r="F25" t="n">
-        <v>23.87910725356479</v>
+        <v>171.48278983261</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>7.351969981238274</v>
+        <v>364.7024240150093</v>
       </c>
       <c r="I25" t="n">
-        <v>-10.2027111105235</v>
+        <v>174.5229498216677</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -1401,28 +1407,28 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.355123320633647</v>
+        <v>88.1899238018849</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>16.4683273421703</v>
       </c>
       <c r="F26" t="n">
-        <v>1.358156911581569</v>
+        <v>21.93584806973848</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>9.426756088951642</v>
+        <v>155.2429050476527</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.106230866602921</v>
+        <v>-86.71685482625803</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1439,24 +1445,24 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.40844250363901</v>
+        <v>13.21760815138282</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>5.488031427535356</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9523672332661097</v>
+        <v>4.914240105850593</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>2.607887022034486</v>
+        <v>14.31216593638685</v>
       </c>
       <c r="I27" t="n">
-        <v>-56.4224653763816</v>
+        <v>-90.95098020104693</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1477,28 +1483,28 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5.605681818181818</v>
+        <v>32.11468181818181</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>5.728951956213257</v>
       </c>
       <c r="F28" t="n">
-        <v>4.797522426313542</v>
+        <v>24.72739854762922</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>5.663605051664753</v>
+        <v>32.44652123995407</v>
       </c>
       <c r="I28" t="n">
-        <v>1.427288860627307</v>
+        <v>-37.06256973394611</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1515,24 +1521,24 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7.471132897603486</v>
+        <v>879.6452450980391</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
+        <v>117.7392046365823</v>
       </c>
       <c r="F29" t="n">
-        <v>5.365519937451134</v>
+        <v>631.3669546520719</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>7.471132897603486</v>
+        <v>879.6452450980391</v>
       </c>
       <c r="I29" t="n">
-        <v>35.18012243640798</v>
+        <v>32.49195586422942</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1553,28 +1559,28 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9.847902097902098</v>
+        <v>345.0829245754246</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>35.04126271207933</v>
       </c>
       <c r="F30" t="n">
-        <v>23.48275862068965</v>
+        <v>735.5681856763925</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>19.38593903638152</v>
+        <v>679.3077826941986</v>
       </c>
       <c r="I30" t="n">
-        <v>78.18457114625635</v>
+        <v>-16.53886183415564</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1591,28 +1597,28 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.874264705882353</v>
+        <v>1122.459180147059</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>163.2842533960851</v>
       </c>
       <c r="F31" t="n">
-        <v>4.309651474530831</v>
+        <v>682.2343543342271</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>7.862910008410429</v>
+        <v>1283.889390243902</v>
       </c>
       <c r="I31" t="n">
-        <v>24.38059359103817</v>
+        <v>360.828981493594</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -1629,28 +1635,28 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.644089574155654</v>
+        <v>448.2017767988252</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>79.41081921363296</v>
       </c>
       <c r="F32" t="n">
-        <v>4.283840693057394</v>
+        <v>294.3878329924196</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>6.8224983359219</v>
+        <v>541.7801819392056</v>
       </c>
       <c r="I32" t="n">
-        <v>2.122225656185606</v>
+        <v>-32.49195586422942</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1667,28 +1673,28 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>4.446813495782568</v>
+        <v>52.10680178069353</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>11.71778439327678</v>
       </c>
       <c r="F33" t="n">
-        <v>4.334302325581396</v>
+        <v>49.82017665474061</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>6.513040494166095</v>
+        <v>76.31840425531914</v>
       </c>
       <c r="I33" t="n">
-        <v>-19.54087806354237</v>
+        <v>-78.60739631499149</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1705,24 +1711,24 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6.67160558010571</v>
+        <v>132.7326548825925</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>19.89515916204527</v>
       </c>
       <c r="F34" t="n">
-        <v>5.886022402287893</v>
+        <v>92.56801537178265</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>7.775118650913864</v>
+        <v>154.6872230637181</v>
       </c>
       <c r="I34" t="n">
-        <v>20.71374870809817</v>
+        <v>11.46292769384138</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1743,24 +1749,24 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-27.81015452538631</v>
+        <v>-2931.119646799117</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>105.3974599142721</v>
       </c>
       <c r="F35" t="n">
-        <v>5.280373831775701</v>
+        <v>444.2654205607477</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>7.065619742007852</v>
+        <v>744.6983735277622</v>
       </c>
       <c r="I35" t="n">
-        <v>-603.1874208693361</v>
+        <v>-5844.324026509199</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1781,28 +1787,28 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.19820545266306</v>
+        <v>55.09626366041643</v>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>5.402544978737324</v>
       </c>
       <c r="F36" t="n">
-        <v>8.209408856249546</v>
+        <v>22.39899730967789</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>8.931392303042514</v>
+        <v>48.25224863993552</v>
       </c>
       <c r="I36" t="n">
-        <v>84.52284019266314</v>
+        <v>-81.94707079219583</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1819,28 +1825,28 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0.02348914069877243</v>
+        <v>312.0416501416431</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>13284.50683417085</v>
       </c>
       <c r="F37" t="n">
-        <v>0.03234880450070324</v>
+        <v>265.5957263411694</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>0.03424539666150404</v>
+        <v>454.9332059886422</v>
       </c>
       <c r="I37" t="n">
-        <v>-99.57499552489494</v>
+        <v>2.24406240346684</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1857,28 +1863,28 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.319285714285714</v>
+        <v>1801.077764285714</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>338.5939129850947</v>
       </c>
       <c r="F38" t="n">
-        <v>3.859561752988048</v>
+        <v>1255.882405378486</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>6.226588628762542</v>
+        <v>2108.285008361204</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.754664254194706</v>
+        <v>490.1439991793895</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -1895,28 +1901,28 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.995493122622183</v>
+        <v>24.14944629792215</v>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>6.044171659610623</v>
       </c>
       <c r="F39" t="n">
-        <v>2.944468753729265</v>
+        <v>16.64152472254266</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>4.598383294038396</v>
+        <v>27.79341798585382</v>
       </c>
       <c r="I39" t="n">
-        <v>-27.70691447837259</v>
+        <v>-39.88691986361034</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1926,31 +1932,35 @@
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HDFC Bank Ltd</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
           <t>Financials</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6.324077153308946</v>
+        <v>11.20107291320253</v>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>1.771179041884679</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2997247693062</v>
+        <v>19.00820852487027</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>9.889618409933043</v>
+        <v>17.51628485991029</v>
       </c>
       <c r="I40" t="n">
-        <v>11.6466572184976</v>
+        <v>-87.81322771219565</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -1971,24 +1981,24 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8.394962793360046</v>
+        <v>26.91906124785346</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>3.206573026046638</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1560850791620022</v>
+        <v>0.4795458180073565</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>10.72076023391813</v>
+        <v>34.37690058479532</v>
       </c>
       <c r="I41" t="n">
-        <v>48.20653047566041</v>
+        <v>-70.71204944640851</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -2005,28 +2015,28 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4.282361480764578</v>
+        <v>385.5313041374304</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>90.02773490027684</v>
       </c>
       <c r="F42" t="n">
-        <v>0.5300112922373107</v>
+        <v>46.15359990734574</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>6.028269754768393</v>
+        <v>542.7114713896458</v>
       </c>
       <c r="I42" t="n">
-        <v>-22.51641655679776</v>
+        <v>58.28103271984683</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -2043,28 +2053,28 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8.499839846252403</v>
+        <v>57.83801249199231</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>6.804600267556007</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8287239847618659</v>
+        <v>3.970875682732665</v>
       </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>10.45258493353028</v>
+        <v>71.12566223535204</v>
       </c>
       <c r="I43" t="n">
-        <v>53.79319399803833</v>
+        <v>-60.40302343829295</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -2081,24 +2091,24 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.761364692758204</v>
+        <v>51.02636329831737</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>10.71675172790816</v>
       </c>
       <c r="F44" t="n">
-        <v>1.100204584359735</v>
+        <v>11.4895952152311</v>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>5.049590850833087</v>
+        <v>54.1152114758947</v>
       </c>
       <c r="I44" t="n">
-        <v>-13.84949632767141</v>
+        <v>0</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2123,24 +2133,24 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.886752136752137</v>
+        <v>25.16830471611722</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>5.150313339371604</v>
       </c>
       <c r="F45" t="n">
-        <v>15.16959641112932</v>
+        <v>23.62537869267113</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>7.223259355348129</v>
+        <v>37.2020490115902</v>
       </c>
       <c r="I45" t="n">
-        <v>-13.7281966210267</v>
+        <v>-72.61687332792323</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -2161,24 +2171,24 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5.411040508339952</v>
+        <v>505.0791143764893</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>93.34232733944954</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6833684421707292</v>
+        <v>63.78720082254991</v>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>7.880277617119722</v>
+        <v>735.5634528629265</v>
       </c>
       <c r="I46" t="n">
-        <v>-4.472293714199926</v>
+        <v>449.5263000187263</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -2199,20 +2209,20 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8829568788501</v>
+        <v>1639.617607802875</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>137.9806073958873</v>
       </c>
       <c r="F47" t="n">
-        <v>0.1498233032582102</v>
+        <v>20.67271038562608</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>13.60047003525264</v>
+        <v>1876.601116333725</v>
       </c>
       <c r="I47" t="n">
-        <v>109.7843497530703</v>
+        <v>1683.904683078715</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2226,31 +2236,35 @@
           <t>INDIGO</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Interglobe Aviation Ltd</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.1506420810009878</v>
+        <v>171.3258017780705</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>1137.303737704918</v>
       </c>
       <c r="F48" t="n">
-        <v>0.01538766345264826</v>
+        <v>17.18151367058513</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-0.1482741857073408</v>
+        <v>-168.6327856101118</v>
       </c>
       <c r="I48" t="n">
-        <v>-97.27433372784455</v>
+        <v>-29.66167845264741</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -2271,24 +2285,24 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7.731716326028072</v>
+        <v>222.5354740211771</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>28.78215710941606</v>
       </c>
       <c r="F49" t="n">
-        <v>24.63196378830084</v>
+        <v>111.4125109430959</v>
       </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>8.497564276048715</v>
+        <v>244.5782300405954</v>
       </c>
       <c r="I49" t="n">
-        <v>36.49743060314423</v>
+        <v>142.1186942420584</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -2305,28 +2319,28 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>3.182576660526601</v>
+        <v>40.17336367248167</v>
       </c>
       <c r="E50" t="n">
-        <v>1</v>
+        <v>12.62290526124654</v>
       </c>
       <c r="F50" t="n">
-        <v>2.529165028181938</v>
+        <v>29.37839612006816</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>3.655052264808362</v>
+        <v>46.13737846358055</v>
       </c>
       <c r="I50" t="n">
-        <v>-42.41554680800252</v>
+        <v>0</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -2343,28 +2357,28 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>16.81336511137593</v>
+        <v>129.9994802456687</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>7.73191323595959</v>
       </c>
       <c r="F51" t="n">
-        <v>9.597479501973885</v>
+        <v>47.09360249013059</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>8.428315412186381</v>
+        <v>65.16700349232607</v>
       </c>
       <c r="I51" t="n">
-        <v>204.2152757117845</v>
+        <v>9.167730274641483</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -2381,28 +2395,28 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.691666666666667</v>
+        <v>1048.766908333333</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>389.6347647058824</v>
       </c>
       <c r="F52" t="n">
-        <v>2.186046511627907</v>
+        <v>836.2659734219269</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>3.210735586481113</v>
+        <v>1251.014204771372</v>
       </c>
       <c r="I52" t="n">
-        <v>-51.29790427436869</v>
+        <v>330.5743983742158</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -2423,24 +2437,24 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.523175768701239</v>
+        <v>400.5428453419</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>53.24119197218325</v>
       </c>
       <c r="F53" t="n">
-        <v>17.23663950967935</v>
+        <v>113.2516473577995</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>7.974541916653154</v>
+        <v>424.5741170747527</v>
       </c>
       <c r="I53" t="n">
-        <v>32.81580946608376</v>
+        <v>335.7907930353198</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -2457,24 +2471,24 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3.577080032646791</v>
+        <v>15.95110566997936</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>4.459253224529239</v>
       </c>
       <c r="F54" t="n">
-        <v>2.808183183183183</v>
+        <v>12.48305480480481</v>
       </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="n">
-        <v>3.825383786004005</v>
+        <v>17.05835498280023</v>
       </c>
       <c r="I54" t="n">
-        <v>-35.27753777032508</v>
+        <v>-68.73948163477024</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2495,28 +2509,28 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>9.355928853754941</v>
+        <v>78.37706916996046</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>8.37726220400921</v>
       </c>
       <c r="F55" t="n">
-        <v>6.256124721603563</v>
+        <v>40.07494625738355</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>9.355928853754941</v>
+        <v>78.37706916996046</v>
       </c>
       <c r="I55" t="n">
-        <v>69.28297559297923</v>
+        <v>-46.34160412535101</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -2526,27 +2540,31 @@
           <t>JIOFIN</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Jio Financial Services Ltd</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>85.34163036714375</v>
+        <v>872.2930864965774</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>10.22119079216007</v>
       </c>
       <c r="F56" t="n">
-        <v>89.57805355976485</v>
+        <v>915.5943762246898</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>85.44797507788162</v>
+        <v>873.3800560747663</v>
       </c>
       <c r="I56" t="n">
-        <v>1444.142260627398</v>
+        <v>849.055264235436</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2567,28 +2585,28 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.47887323943662</v>
+        <v>55.76988430583501</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
+        <v>5.322126056067589</v>
       </c>
       <c r="F57" t="n">
-        <v>9.737086584912673</v>
+        <v>26.46665366034931</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>12.07652173913043</v>
+        <v>64.27277101449275</v>
       </c>
       <c r="I57" t="n">
-        <v>89.60114709738643</v>
+        <v>-53.16695362287647</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -2605,24 +2623,24 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>23.45078502415459</v>
+        <v>788.8425060386473</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>33.63821318672829</v>
       </c>
       <c r="F58" t="n">
-        <v>7.369561348874455</v>
+        <v>120.1454924815375</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>9.865235615394386</v>
+        <v>331.848898767941</v>
       </c>
       <c r="I58" t="n">
-        <v>324.3104806517318</v>
+        <v>440.0562169527381</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2647,24 +2665,24 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5.768841544607191</v>
+        <v>19.0955845539281</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>3.310124642230635</v>
       </c>
       <c r="F59" t="n">
-        <v>12.78396760496934</v>
+        <v>18.68606541909105</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>8.708341708542713</v>
+        <v>28.82569648241206</v>
       </c>
       <c r="I59" t="n">
-        <v>1.844404940820432</v>
+        <v>-79.22399555252071</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -2685,20 +2703,20 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1.99544226873734</v>
+        <v>4.427116571814412</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>2.218614209578595</v>
       </c>
       <c r="F60" t="n">
-        <v>3.20092066070945</v>
+        <v>7.101608061583692</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>2.298719337722588</v>
+        <v>5.099971386504431</v>
       </c>
       <c r="I60" t="n">
-        <v>-64.77202071128252</v>
+        <v>-95.18329521016915</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2719,24 +2737,24 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6.956989247311828</v>
+        <v>481.847865392274</v>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>69.26097601465453</v>
       </c>
       <c r="F61" t="n">
-        <v>6.602046169989507</v>
+        <v>319.4171012591815</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>14.46109271523179</v>
+        <v>1001.589395695364</v>
       </c>
       <c r="I61" t="n">
-        <v>25.87738313985202</v>
+        <v>16.53886183415565</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2757,24 +2775,24 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1.239504643962848</v>
+        <v>69.63452012383901</v>
       </c>
       <c r="E62" t="n">
-        <v>1</v>
+        <v>56.17931361774403</v>
       </c>
       <c r="F62" t="n">
-        <v>0.716826220996268</v>
+        <v>36.56233976959273</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>1.549260893119728</v>
+        <v>87.03641359027939</v>
       </c>
       <c r="I62" t="n">
-        <v>-77.5728270627951</v>
+        <v>-77.18344260214795</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2795,28 +2813,28 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>4.376475732400524</v>
+        <v>294.5008526453869</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>67.29178239584374</v>
       </c>
       <c r="F63" t="n">
-        <v>3.433167547404414</v>
+        <v>209.6857165060615</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>4.53922902494331</v>
+        <v>305.4528117913832</v>
       </c>
       <c r="I63" t="n">
-        <v>-20.81354548844357</v>
+        <v>633.0749176154172</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -2833,24 +2851,24 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5.08801598893074</v>
+        <v>320.7844938119763</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>63.04706874150174</v>
       </c>
       <c r="F64" t="n">
-        <v>6.42688575209528</v>
+        <v>157.3934891927658</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>5.819412695621593</v>
+        <v>366.8969122560225</v>
       </c>
       <c r="I64" t="n">
-        <v>-7.939179536923513</v>
+        <v>31.69903563258634</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
@@ -2871,28 +2889,28 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6.107695599457956</v>
+        <v>107.2579437985878</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>17.56111483488252</v>
       </c>
       <c r="F65" t="n">
-        <v>4.338510573712435</v>
+        <v>76.08937721339673</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>10.36253630203291</v>
+        <v>181.9776899806389</v>
       </c>
       <c r="I65" t="n">
-        <v>10.51055445739384</v>
+        <v>-55.96492961879947</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -2909,28 +2927,28 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6.343681785107931</v>
+        <v>35.44777104050448</v>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>5.587886063850124</v>
       </c>
       <c r="F66" t="n">
-        <v>4.399178919228566</v>
+        <v>15.85575329387054</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>15.66167664670659</v>
+        <v>87.51566467065868</v>
       </c>
       <c r="I66" t="n">
-        <v>14.78040775898581</v>
+        <v>-85.44681132843189</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -2947,24 +2965,24 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>54.92196007259528</v>
+        <v>1023.274845735027</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>18.63143348093318</v>
       </c>
       <c r="F67" t="n">
-        <v>40.62316910785619</v>
+        <v>751.092463382157</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>21.34132581100141</v>
+        <v>397.6194922425952</v>
       </c>
       <c r="I67" t="n">
-        <v>893.7391542643352</v>
+        <v>94.78366812534259</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -2985,28 +3003,28 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1.005115859163407</v>
+        <v>504.8977399939813</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>502.3279011976048</v>
       </c>
       <c r="F68" t="n">
-        <v>0.7797291578501905</v>
+        <v>355.0825624206517</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>1.113704568189396</v>
+        <v>559.4448782927642</v>
       </c>
       <c r="I68" t="n">
-        <v>-81.81377753994066</v>
+        <v>889.4840771665</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -3023,24 +3041,24 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.32630962832894</v>
+        <v>509.3369183494293</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>44.96936204847295</v>
       </c>
       <c r="F69" t="n">
-        <v>14.20997008973081</v>
+        <v>353.5324526420738</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>10.25490196078431</v>
+        <v>461.1563990461049</v>
       </c>
       <c r="I69" t="n">
-        <v>104.9343711716467</v>
+        <v>327.7182894593931</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3061,28 +3079,28 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>7.12809367515302</v>
+        <v>40.26537345870664</v>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>5.648827764295937</v>
       </c>
       <c r="F70" t="n">
-        <v>7.593544816002443</v>
+        <v>21.85360570316078</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>9.386718065533556</v>
+        <v>53.02395362420419</v>
       </c>
       <c r="I70" t="n">
-        <v>28.97328811463879</v>
+        <v>-66.18694612593077</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -3099,28 +3117,28 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>7.964792060491494</v>
+        <v>9.218125000000001</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>1.15735915388495</v>
       </c>
       <c r="F71" t="n">
-        <v>5.709223244439269</v>
+        <v>6.326913357400723</v>
       </c>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>7.964792060491494</v>
+        <v>9.218125000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>44.1122224265529</v>
+        <v>-92.25903225354274</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -3141,24 +3159,24 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3.580678278108185</v>
+        <v>71.2222390965732</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>19.89071163751767</v>
       </c>
       <c r="F72" t="n">
-        <v>26.92953808298848</v>
+        <v>80.3558553293815</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>4.775815666462061</v>
+        <v>94.99437225553615</v>
       </c>
       <c r="I72" t="n">
-        <v>-36.7859134804368</v>
+        <v>-22.51017233586329</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -3175,28 +3193,28 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4.261023821591485</v>
+        <v>82.24743030917384</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>19.30226953729035</v>
       </c>
       <c r="F73" t="n">
-        <v>2.97730352303523</v>
+        <v>55.10033197831978</v>
       </c>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>6.52211016291699</v>
+        <v>125.8915283165244</v>
       </c>
       <c r="I73" t="n">
-        <v>-22.90249286129641</v>
+        <v>-43.69188307319709</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3235,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.027382180942553</v>
+        <v>125.6226762985896</v>
       </c>
       <c r="E74" t="n">
-        <v>1</v>
+        <v>122.2745329136811</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>3.821136131013306</v>
+        <v>467.2276356192426</v>
       </c>
       <c r="I74" t="n">
-        <v>-81.86236767714492</v>
+        <v>36.67752742069727</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -3249,28 +3267,28 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5.546461303462322</v>
+        <v>23.71335539714867</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>4.27540265760907</v>
       </c>
       <c r="F75" t="n">
-        <v>5.369236650949407</v>
+        <v>12.64432878807187</v>
       </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>5.595967379438772</v>
+        <v>23.92501380594619</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3557731293121202</v>
+        <v>-80.08658818473322</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -3287,28 +3305,28 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>4.659052737655358</v>
+        <v>19.61151629156869</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>4.209335544340303</v>
       </c>
       <c r="F76" t="n">
-        <v>10.1242233582383</v>
+        <v>14.50030318521431</v>
       </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>6.210262380227456</v>
+        <v>26.14107817677084</v>
       </c>
       <c r="I76" t="n">
-        <v>-15.70069383775015</v>
+        <v>-78.66266159358663</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -3325,28 +3343,28 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>9.925832801691246</v>
+        <v>5.409898675273014</v>
       </c>
       <c r="E77" t="n">
-        <v>1</v>
+        <v>0.5450322187928885</v>
       </c>
       <c r="F77" t="n">
-        <v>7.631068434392669</v>
+        <v>5.431515097972314</v>
       </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>10.70998002375553</v>
+        <v>5.837284175574992</v>
       </c>
       <c r="I77" t="n">
-        <v>79.59462263699501</v>
+        <v>-95.45700984127572</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -3367,24 +3385,24 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>6.183326420572377</v>
+        <v>367.5228992119452</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>59.43773209015293</v>
       </c>
       <c r="F78" t="n">
-        <v>14.80436941410129</v>
+        <v>879.9381429990069</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>8.662405578152237</v>
+        <v>514.8737420104591</v>
       </c>
       <c r="I78" t="n">
-        <v>9.161812642736876</v>
+        <v>299.8650770293991</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -3405,18 +3423,18 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
+        <v>32.23749412444098</v>
       </c>
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="n">
-        <v>-0</v>
+        <v>-40.55475671566143</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>41.56599220779221</v>
       </c>
       <c r="I79" t="n">
-        <v>-100</v>
+        <v>-64.9255921224366</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3437,24 +3455,24 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.9463358338142</v>
+        <v>1820.172146566647</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>152.3623788822876</v>
       </c>
       <c r="F80" t="n">
-        <v>5.290818741126361</v>
+        <v>746.8088807382868</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>11.9463358338142</v>
+        <v>1820.172146566647</v>
       </c>
       <c r="I80" t="n">
-        <v>116.1529131946595</v>
+        <v>1146.123625632021</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3479,20 +3497,20 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>5.177385233763486</v>
+        <v>91.91172731119103</v>
       </c>
       <c r="E81" t="n">
-        <v>1</v>
+        <v>17.75253784705906</v>
       </c>
       <c r="F81" t="n">
-        <v>21.41231604765242</v>
+        <v>93.24014278206026</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>8.130730897009967</v>
+        <v>144.3411079734219</v>
       </c>
       <c r="I81" t="n">
-        <v>-8.597295626025625</v>
+        <v>0</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3513,26 +3531,26 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5.650110375275938</v>
+        <v>438.3119757174393</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>77.57582535651494</v>
       </c>
       <c r="F82" t="n">
-        <v>5.037371134020619</v>
+        <v>383.8952802835051</v>
       </c>
       <c r="G82" t="n">
-        <v>7.605652145601355</v>
+        <v>0.09804152402695152</v>
       </c>
       <c r="H82" t="n">
-        <v>9.952689565780947</v>
+        <v>772.0881075826312</v>
       </c>
       <c r="I82" t="n">
-        <v>2.231163971667383</v>
+        <v>43.61799771632477</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3553,28 +3571,28 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5.726994692812809</v>
+        <v>120.4988836916434</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>21.04050905492641</v>
       </c>
       <c r="F83" t="n">
-        <v>4.761433956895939</v>
+        <v>95.51604594921403</v>
       </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>7.478797133795371</v>
+        <v>157.3576988135792</v>
       </c>
       <c r="I83" t="n">
-        <v>3.62228250757346</v>
+        <v>-81.85048703584731</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Discount</t>
         </is>
       </c>
     </row>
@@ -3591,24 +3609,24 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.72393162393162</v>
+        <v>299.6097008547009</v>
       </c>
       <c r="E84" t="n">
-        <v>1</v>
+        <v>21.83118577567416</v>
       </c>
       <c r="F84" t="n">
-        <v>7.826121794871795</v>
+        <v>141.8350761217949</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>13.72393162393162</v>
+        <v>299.6097008547009</v>
       </c>
       <c r="I84" t="n">
-        <v>148.3161232250415</v>
+        <v>487.16647922385</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3629,24 +3647,24 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>2.988585285072155</v>
+        <v>44.47914123491838</v>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>14.8830088460549</v>
       </c>
       <c r="F85" t="n">
-        <v>3.431756946625453</v>
+        <v>26.62372745755988</v>
       </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>2.988585285072155</v>
+        <v>44.47914123491838</v>
       </c>
       <c r="I85" t="n">
-        <v>-45.92556038224252</v>
+        <v>-81.73895521945688</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3667,28 +3685,28 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>7.348625936861231</v>
+        <v>374.1243424937542</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>50.9107887254296</v>
       </c>
       <c r="F86" t="n">
-        <v>7.781948087184589</v>
+        <v>153.8354418015737</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>8.492388451443569</v>
+        <v>432.3541942257218</v>
       </c>
       <c r="I86" t="n">
-        <v>32.96352340391555</v>
+        <v>214.1728354094441</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -3705,28 +3723,28 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>36.42065690542145</v>
+        <v>146.0667392164622</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>4.010546531210952</v>
       </c>
       <c r="F87" t="n">
-        <v>7.075807853361776</v>
+        <v>18.02135774670143</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>11.23748473748474</v>
+        <v>45.06845543345543</v>
       </c>
       <c r="I87" t="n">
-        <v>558.9829048909759</v>
+        <v>0</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -3743,24 +3761,24 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1.846488185120189</v>
+        <v>9.410850712157696</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>5.096621136270707</v>
       </c>
       <c r="F88" t="n">
-        <v>1.457442558920566</v>
+        <v>6.941887973250877</v>
       </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>2.139068151194951</v>
+        <v>10.90201995130369</v>
       </c>
       <c r="I88" t="n">
-        <v>-66.59027454564557</v>
+        <v>-76.57440191246911</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3781,28 +3799,28 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>7.064635761589404</v>
+        <v>800.2902357615894</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>113.2811743972402</v>
       </c>
       <c r="F89" t="n">
-        <v>4.69323477422465</v>
+        <v>485.8802249718785</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>6.126579370549047</v>
+        <v>694.026106133701</v>
       </c>
       <c r="I89" t="n">
-        <v>27.82510233844411</v>
+        <v>1892.091681159822</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Fair</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -3819,28 +3837,28 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2.896392229417206</v>
+        <v>553.1204810360776</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
+        <v>190.9687767486426</v>
       </c>
       <c r="F90" t="n">
-        <v>4.756823821339951</v>
+        <v>345.3517312464211</v>
       </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>2.896392229417206</v>
+        <v>553.1204810360776</v>
       </c>
       <c r="I90" t="n">
-        <v>-47.59366998784466</v>
+        <v>127.085271720712</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -3857,28 +3875,28 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>3.682062298603652</v>
+        <v>1004.387964554243</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>272.778644982497</v>
       </c>
       <c r="F91" t="n">
-        <v>2.988461538461539</v>
+        <v>514.8880192307691</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>5.476038338658147</v>
+        <v>1493.746317891374</v>
       </c>
       <c r="I91" t="n">
-        <v>-33.37802456928801</v>
+        <v>51.28067435350317</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Caution</t>
         </is>
       </c>
     </row>
@@ -3895,28 +3913,28 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>2.248756218905473</v>
+        <v>315.8220232172471</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>140.4429793510324</v>
       </c>
       <c r="F92" t="n">
-        <v>2.472812234494477</v>
+        <v>243.4473406966865</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>2.754231550440081</v>
+        <v>386.8124847664184</v>
       </c>
       <c r="I92" t="n">
-        <v>-59.31177437644222</v>
+        <v>29.66167845264742</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -3933,24 +3951,24 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Diversified</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>3.239732569245463</v>
+        <v>127.3120391595033</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
+        <v>39.29708284198113</v>
       </c>
       <c r="F93" t="n">
-        <v>5.297253634894992</v>
+        <v>47.26937156704361</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>5.182582123758595</v>
+        <v>203.660359052712</v>
       </c>
       <c r="I93" t="n">
-        <v>-41.38138735126762</v>
+        <v>-47.7316606470625</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4002,25 +4020,15 @@
           <t>Diversified</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>9.815259117082533</v>
-      </c>
-      <c r="E95" t="n">
-        <v>1</v>
-      </c>
-      <c r="F95" t="n">
-        <v>6.497096881220969</v>
-      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
-      <c r="H95" t="n">
-        <v>9.815259117082533</v>
-      </c>
-      <c r="I95" t="n">
-        <v>77.59394021994883</v>
-      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -4037,25 +4045,15 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>5.971488007831621</v>
-      </c>
-      <c r="E96" t="n">
-        <v>1</v>
-      </c>
-      <c r="F96" t="n">
-        <v>645.533971291866</v>
-      </c>
+          <t>Diversified</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
-      <c r="H96" t="n">
-        <v>11.46593045112782</v>
-      </c>
-      <c r="I96" t="n">
-        <v>5.421970436573575</v>
-      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr">
         <is>
           <t>Fair</t>
@@ -4078,22 +4076,12 @@
           <t>Diversified</t>
         </is>
       </c>
-      <c r="D97" t="n">
-        <v>5.079172610556348</v>
-      </c>
-      <c r="E97" t="n">
-        <v>1</v>
-      </c>
-      <c r="F97" t="n">
-        <v>3.498815727143534</v>
-      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
-      <c r="H97" t="n">
-        <v>6.324156305506217</v>
-      </c>
-      <c r="I97" t="n">
-        <v>-8.09918859950962</v>
-      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
           <t>Fair</t>
@@ -4116,23 +4104,15 @@
           <t>Diversified</t>
         </is>
       </c>
-      <c r="D98" t="n">
-        <v>0</v>
-      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
-      <c r="F98" t="n">
-        <v>0</v>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
-      <c r="H98" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" t="n">
-        <v>-100</v>
-      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -4152,25 +4132,15 @@
           <t>Diversified</t>
         </is>
       </c>
-      <c r="D99" t="n">
-        <v>1.939397765292595</v>
-      </c>
-      <c r="E99" t="n">
-        <v>1</v>
-      </c>
-      <c r="F99" t="n">
-        <v>3.194540353905913</v>
-      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
-      <c r="H99" t="n">
-        <v>2.043773283661522</v>
-      </c>
-      <c r="I99" t="n">
-        <v>-64.90920039058004</v>
-      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Discount</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -4190,22 +4160,12 @@
           <t>Diversified</t>
         </is>
       </c>
-      <c r="D100" t="n">
-        <v>5.968369634849456</v>
-      </c>
-      <c r="E100" t="n">
-        <v>1</v>
-      </c>
-      <c r="F100" t="n">
-        <v>5.1200135036291</v>
-      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="n">
-        <v>6.557540031673412</v>
-      </c>
-      <c r="I100" t="n">
-        <v>7.989638123488296</v>
-      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr">
         <is>
           <t>Fair</t>
@@ -4228,25 +4188,15 @@
           <t>Diversified</t>
         </is>
       </c>
-      <c r="D101" t="n">
-        <v>30.78883861236802</v>
-      </c>
-      <c r="E101" t="n">
-        <v>1</v>
-      </c>
-      <c r="F101" t="n">
-        <v>32.50691244239631</v>
-      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
-      <c r="H101" t="n">
-        <v>-16.70458265139116</v>
-      </c>
-      <c r="I101" t="n">
-        <v>457.0827115964933</v>
-      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Caution</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -4266,22 +4216,12 @@
           <t>Diversified</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>4.467222347375535</v>
-      </c>
-      <c r="E102" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" t="n">
-        <v>3.286715514495062</v>
-      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
-      <c r="H102" t="n">
-        <v>4.991190536118802</v>
-      </c>
-      <c r="I102" t="n">
-        <v>-19.17160728561138</v>
-      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>Fair</t>
